--- a/tests/fixtures/expected/export_final.xlsx
+++ b/tests/fixtures/expected/export_final.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1A" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2B" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="10A" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1A" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2B" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10A" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,19 +438,19 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Jenis Kelamin</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>NIM</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Prodi</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Kelas Umum</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Kode Kelas PAI</t>
@@ -458,35 +458,30 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Dosen Pengampu</t>
+          <t>PRESENSI</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>PRESENSI</t>
+          <t>BACAAN</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>BACAAN</t>
+          <t>HAFALAN</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>HAFALAN</t>
+          <t>EVALUASI</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>EVALUASI</t>
+          <t>TOTAL NILAI</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL NILAI</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>ABJAD</t>
         </is>
@@ -500,19 +495,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>240001</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Teknik Informatika</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>TI-A</t>
-        </is>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>1A</t>
@@ -520,35 +515,30 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dr. Ana</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>87</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>92</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>89</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -562,35 +552,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>240002</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Teknik Informatika</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>TI-A</t>
-        </is>
-      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Dr. Ana</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -603,7 +588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -614,19 +599,19 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Jenis Kelamin</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>NIM</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Prodi</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Kelas Umum</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Kode Kelas PAI</t>
@@ -634,35 +619,30 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Dosen Pengampu</t>
+          <t>PRESENSI</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>PRESENSI</t>
+          <t>BACAAN</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>BACAAN</t>
+          <t>HAFALAN</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>HAFALAN</t>
+          <t>EVALUASI</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>EVALUASI</t>
+          <t>TOTAL NILAI</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL NILAI</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>ABJAD</t>
         </is>
@@ -676,19 +656,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>240003</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Sistem Informasi</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>SI-B</t>
-        </is>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>2B</t>
@@ -696,22 +676,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dr. Bima</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>80</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>85</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,11 +700,6 @@
         </is>
       </c>
       <c r="K2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -738,19 +713,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>240004</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Sistem Informasi</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>SI-B</t>
-        </is>
-      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>2B</t>
@@ -758,35 +733,30 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dr. Bima</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>85</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>82</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -803,7 +773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -814,19 +784,19 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Jenis Kelamin</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>NIM</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Prodi</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Kelas Umum</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Kode Kelas PAI</t>
@@ -834,35 +804,30 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Dosen Pengampu</t>
+          <t>PRESENSI</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>PRESENSI</t>
+          <t>BACAAN</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>BACAAN</t>
+          <t>HAFALAN</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>HAFALAN</t>
+          <t>EVALUASI</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>EVALUASI</t>
+          <t>TOTAL NILAI</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL NILAI</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>ABJAD</t>
         </is>
@@ -876,19 +841,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>240005</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Manajemen</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>MN-A</t>
-        </is>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>10A</t>
@@ -896,7 +861,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dr. Citra</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -914,13 +879,8 @@
           <t>90</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -934,35 +894,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>240006</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Manajemen</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>MN-A</t>
-        </is>
-      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>10A</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Dr. Citra</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
